--- a/BWI/bestwine_output/bestwine_Uruguay.xlsx
+++ b/BWI/bestwine_output/bestwine_Uruguay.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA69"/>
+  <dimension ref="A1:AA71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8047,6 +8047,216 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Hamfer Ltda</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Hamfer Ltda</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>87097</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Montevideo</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Montevideo, CH</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>3181 4 de Julio</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>11600</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://hamfer.com.uy</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>info@hamfer.com.uy</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>+598 2622 8650</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>212486230011</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hamfer.uy/</t>
+        </is>
+      </c>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr"/>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>Adrian Hamburger</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Z70" s="2" t="inlineStr"/>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adrian-hamburger-89159039/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Hamfer Ltda</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Hamfer Ltda</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>87097</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Montevideo</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Montevideo, CH</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>3181 4 de Julio</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>11600</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>https://hamfer.com.uy</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>info@hamfer.com.uy</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>+598 2622 8650</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>212486230011</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hamfer.uy/</t>
+        </is>
+      </c>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr"/>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>Ronald Hamburger</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" s="2" t="inlineStr"/>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ronald-hamburger-5a4b9427</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Uruguay.xlsx
+++ b/BWI/bestwine_output/bestwine_Uruguay.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA71"/>
+  <dimension ref="A1:AA75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8257,6 +8257,430 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Iberpark S.a.</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Iberpark S.a.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>15131</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Montevideo</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Montevideo</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>1249 Soriano</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>11100</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://iber.uy</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>sitioweb@iber.uy</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>213094250019</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/iberpark/</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/iber.uy/</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/iber.uy/</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr"/>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>Nicolás Domínguez</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr"/>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicol%C3%A1s-dom%C3%ADnguez-115391251/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Cava Privada Club De Vinos</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Cava Privada Club De Vinos</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>87183</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Montevideo</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Montevideo, B</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>1150 Maldonado</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>11100</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>https://cavaprivada.com.uy</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>info@cavaprivada.com.uy</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>+598 2908 3430</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavaprivada.com.uy</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cava_privada/</t>
+        </is>
+      </c>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@cavaprivadaclubdevinos5903</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>Martín Guerra</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mart%C3%ADn-guerra-b9bb707/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Hamfer Ltda</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Hamfer Ltda</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>87097</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Montevideo</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Montevideo, CH</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>3181 4 de Julio</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>11600</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://hamfer.com.uy</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>info@hamfer.com.uy</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>+598 2622 8650</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>212486230011</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hamfer.uy/</t>
+        </is>
+      </c>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr"/>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>Adrian Hamburger</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr"/>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adrian-hamburger-89159039/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Hamfer Ltda</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Hamfer Ltda</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>87097</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Montevideo</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Montevideo, CH</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>3181 4 de Julio</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>11600</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>https://hamfer.com.uy</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>info@hamfer.com.uy</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>+598 2622 8650</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>212486230011</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hamfer.uy/</t>
+        </is>
+      </c>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>Ronald Hamburger</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="2" t="inlineStr"/>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ronald-hamburger-5a4b9427</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Uruguay.xlsx
+++ b/BWI/bestwine_output/bestwine_Uruguay.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA75"/>
+  <dimension ref="A1:AA76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8681,6 +8681,115 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Barão Free Shop</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Barão Free Shop</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>86909</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Rivera</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Rivera</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1071 Paysandú</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.baraofreeshop.com.br</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>barao.e.voce@adinet.com.uy</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>+598 4623 9211</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>140041780014</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/baraofshop/</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/baraofreeshop/</t>
+        </is>
+      </c>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCaW-VUIYMEKiADUfZNBL1FQ</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>Sabrina Barão</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="2" t="inlineStr"/>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sabrina-bar%C3%A3o-38b75b90/?originalSubdomain=uy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Uruguay.xlsx
+++ b/BWI/bestwine_output/bestwine_Uruguay.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA76"/>
+  <dimension ref="A1:AA78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8790,6 +8790,228 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Lumien Ltda</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Lumien Ltda</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>86912</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Rivera</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Rivera</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>514 Agraciada</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yurysfreeshop.com</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>seoyuryfreeshop@gmail.com</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>+598 4623 5851</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>140047690017</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/yurysfreeshop/</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yurysfreeshop/</t>
+        </is>
+      </c>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/yurysfreeshop</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCQNAcDIkqiyVcUO4VrnrNpQ</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>Vanessa Borges</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr"/>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vanessa-borges-82137b4b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Barão Free Shop</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Barão Free Shop</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>86909</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Rivera</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Rivera</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>1071 Paysandú</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.baraofreeshop.com.br</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>barao.e.voce@adinet.com.uy</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>+598 4623 9211</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>140041780014</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/baraofshop/</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/baraofreeshop/</t>
+        </is>
+      </c>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCaW-VUIYMEKiADUfZNBL1FQ</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>Sabrina Barão</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr"/>
+      <c r="Z78" s="2" t="inlineStr"/>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sabrina-bar%C3%A3o-38b75b90/?originalSubdomain=uy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Uruguay.xlsx
+++ b/BWI/bestwine_output/bestwine_Uruguay.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA78"/>
+  <dimension ref="A1:AA81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -9012,6 +9012,313 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Urfix S.a.</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Urfix S.a.</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>87066</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Chuy</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Rocha, Chuí</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>285 Avenida Brasil</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>27100</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.neutral.com.uy</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>info@neutral.com.uy</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>+598 4474 2277</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>210321770013</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/neutral-s.a/</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/neutraldutyfree</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/NeutralDutyFree/</t>
+        </is>
+      </c>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr"/>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>Magdalena Pereyra</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr"/>
+      <c r="Z79" s="2" t="inlineStr"/>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/magdalena-pereyra-94083868/?originalSubdomain=uy</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Suchina S.a</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Suchina S.a</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>87116</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Montevideo</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>2883 Montevideo</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>https://suchinasa.com</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>contacto@suchinasa.com</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>+598 2200 4000</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/suchina-s-a/</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SUImportadorMayorista/</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/suchinauy/</t>
+        </is>
+      </c>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/suchinauy</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCRfIcvG67U5_tP8rF2QKCGw</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>Daniel García</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>Sales Assistant</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr"/>
+      <c r="Z80" s="2" t="inlineStr"/>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniel-garc%C3%ADa-522402212/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Sluckis Hnos. S.a.</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Sluckis Hnos. S.a.</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>86366</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Montevideo</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Montevideo, C</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>2193 Arenal Grande</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>11800</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>atencionalcliente@sluckis.com.uy</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>+598 2929 1515</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>210301960011</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sluckis-hnos-s-a/</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sluckishnos</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sluckishnos/</t>
+        </is>
+      </c>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr"/>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>Fabricio Morencio</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr"/>
+      <c r="Z81" s="2" t="inlineStr"/>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fabricio-morencio-2ab0b390/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Uruguay.xlsx
+++ b/BWI/bestwine_output/bestwine_Uruguay.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA81"/>
+  <dimension ref="A1:AA83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -9319,6 +9319,232 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Devoto Hnos Sa</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Devoto Hnos Sa</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>106539</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Montevideo</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Montevideo, CH</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>2627 Jaime Zudáñez</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>11300</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.devoto.com.uy</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>atencionalcliente@devoto.com.uy</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>+598 800 0033</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>210297450018</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mercados-devoto-s.a./</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DevotoOficial</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/devotouy</t>
+        </is>
+      </c>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/devoto_uy</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr"/>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>Ramon Pante</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Assistant</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr"/>
+      <c r="Z82" s="2" t="inlineStr"/>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ramon-pante-466435273/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Devoto Hnos Sa</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Devoto Hnos Sa</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>106539</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Montevideo</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Montevideo, CH</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>2627 Jaime Zudáñez</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>11300</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.devoto.com.uy</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>atencionalcliente@devoto.com.uy</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>+598 800 0033</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>210297450018</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mercados-devoto-s.a./</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DevotoOficial</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/devotouy</t>
+        </is>
+      </c>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/devoto_uy</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr"/>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Zamora</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr"/>
+      <c r="Z83" s="2" t="inlineStr"/>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jorge-zamora-caetano-26373b187/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
